--- a/reports/FR-09_domain_test_cases.xlsx
+++ b/reports/FR-09_domain_test_cases.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Cases'!$A$1:$I$32</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Variables!$A$1:$D$10</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -785,11 +785,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1863,7 +1863,7 @@
       <c r="G19" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="H19" s="7" t="s">
         <v>203</v>
       </c>
       <c r="I19" s="8" t="s">
@@ -1892,7 +1892,7 @@
       <c r="G20" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="H20" s="6"/>
+      <c r="H20" s="7"/>
       <c r="I20" s="9"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -1917,7 +1917,7 @@
       <c r="G21" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="H21" s="6"/>
+      <c r="H21" s="7"/>
       <c r="I21" s="10"/>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
@@ -2200,7 +2200,7 @@
       <c r="I32" s="4"/>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A34" s="7"/>
+      <c r="A34" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:I32"/>
